--- a/Employee_Reports_wi48/Nhar Jaradal Cillo Q0494.xlsx
+++ b/Employee_Reports_wi48/Nhar Jaradal Cillo Q0494.xlsx
@@ -578,11 +578,11 @@
         </is>
       </c>
       <c r="H3" s="3" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I3" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J3" s="3" t="inlineStr">
@@ -627,11 +627,11 @@
         </is>
       </c>
       <c r="H4" s="3" t="n">
-        <v>102</v>
+        <v>99</v>
       </c>
       <c r="I4" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J4" s="3" t="inlineStr">
@@ -676,11 +676,11 @@
         </is>
       </c>
       <c r="H5" s="3" t="n">
-        <v>104</v>
+        <v>101</v>
       </c>
       <c r="I5" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J5" s="3" t="inlineStr">
@@ -725,11 +725,11 @@
         </is>
       </c>
       <c r="H6" s="3" t="n">
-        <v>463</v>
+        <v>460</v>
       </c>
       <c r="I6" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J6" s="3" t="inlineStr">
@@ -774,11 +774,11 @@
         </is>
       </c>
       <c r="H7" s="3" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I7" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J7" s="3" t="inlineStr">
@@ -823,11 +823,11 @@
         </is>
       </c>
       <c r="H8" s="3" t="n">
-        <v>400</v>
+        <v>397</v>
       </c>
       <c r="I8" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J8" s="3" t="inlineStr">
@@ -872,11 +872,11 @@
         </is>
       </c>
       <c r="H9" s="3" t="n">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="I9" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J9" s="3" t="inlineStr">
@@ -921,11 +921,11 @@
         </is>
       </c>
       <c r="H10" s="3" t="n">
-        <v>100</v>
+        <v>97</v>
       </c>
       <c r="I10" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J10" s="3" t="inlineStr">
@@ -970,11 +970,11 @@
         </is>
       </c>
       <c r="H11" s="3" t="n">
-        <v>461</v>
+        <v>458</v>
       </c>
       <c r="I11" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J11" s="3" t="inlineStr">
@@ -1019,11 +1019,11 @@
         </is>
       </c>
       <c r="H12" s="3" t="n">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="I12" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J12" s="3" t="inlineStr">
@@ -1068,11 +1068,11 @@
         </is>
       </c>
       <c r="H13" s="3" t="n">
-        <v>334</v>
+        <v>331</v>
       </c>
       <c r="I13" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J13" s="3" t="inlineStr">
@@ -1117,11 +1117,11 @@
         </is>
       </c>
       <c r="H14" s="4" t="n">
-        <v>-283</v>
+        <v>-286</v>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1167,11 +1167,11 @@
         </is>
       </c>
       <c r="H15" s="4" t="n">
-        <v>-402</v>
+        <v>-405</v>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
@@ -1216,11 +1216,11 @@
         </is>
       </c>
       <c r="H16" s="4" t="n">
-        <v>-642</v>
+        <v>-645</v>
       </c>
       <c r="I16" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J16" s="4" t="inlineStr">
@@ -1265,11 +1265,11 @@
         </is>
       </c>
       <c r="H17" s="4" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -1302,11 +1302,11 @@
         </is>
       </c>
       <c r="H18" s="4" t="n">
-        <v>-347</v>
+        <v>-350</v>
       </c>
       <c r="I18" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J18" s="4" t="inlineStr">
@@ -1351,11 +1351,11 @@
         </is>
       </c>
       <c r="H19" s="4" t="n">
-        <v>-129</v>
+        <v>-132</v>
       </c>
       <c r="I19" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J19" s="4" t="inlineStr">
@@ -1400,11 +1400,11 @@
         </is>
       </c>
       <c r="H20" s="4" t="n">
-        <v>-144</v>
+        <v>-147</v>
       </c>
       <c r="I20" s="4" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J20" s="4" t="inlineStr">
@@ -1449,11 +1449,11 @@
         </is>
       </c>
       <c r="H21" s="5" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I21" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J21" s="5" t="inlineStr">
@@ -1498,11 +1498,11 @@
         </is>
       </c>
       <c r="H22" s="5" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="I22" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J22" s="5" t="inlineStr">
@@ -1547,11 +1547,11 @@
         </is>
       </c>
       <c r="H23" s="5" t="n">
-        <v>36</v>
+        <v>33</v>
       </c>
       <c r="I23" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J23" s="5" t="inlineStr">
@@ -1596,11 +1596,11 @@
         </is>
       </c>
       <c r="H24" s="5" t="n">
-        <v>37</v>
+        <v>34</v>
       </c>
       <c r="I24" s="5" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J24" s="5" t="inlineStr">
@@ -1633,11 +1633,11 @@
         </is>
       </c>
       <c r="H25" s="3" t="n">
-        <v>456</v>
+        <v>453</v>
       </c>
       <c r="I25" s="3" t="inlineStr">
         <is>
-          <t>12-Jul-2026</t>
+          <t>15-Jul-2026</t>
         </is>
       </c>
       <c r="J25" s="3" t="inlineStr">
